--- a/ML_dataset_smapled/VLOOKUP 함수용 표.xlsx
+++ b/ML_dataset_smapled/VLOOKUP 함수용 표.xlsx
@@ -8,22 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LG\OneDrive\Desktop\REF_Classification_For_Ingredient_Recognition\ML_dataset_smapled\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABA3857-74B7-497D-91AE-CE5E0839B407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32AD6DC-326B-46F2-97D6-0587618E8526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7605" yWindow="465" windowWidth="18510" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="465" windowWidth="18510" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VLOOKUP 함수용 카테고리" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="카테고리표">'VLOOKUP 함수용 카테고리'!$A$1:$B$54</definedName>
+    <definedName name="카테고리표1">'VLOOKUP 함수용 카테고리'!$A$1:$B$55</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="80">
   <si>
     <t>ALCOHOL</t>
   </si>
@@ -246,6 +260,30 @@
   </si>
   <si>
     <t>SAUCE_SEASONING</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>떡</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SNACK</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>양고기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>RAW_MEAT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>면류</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRAIN</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -253,7 +291,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -281,6 +319,13 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -302,10 +347,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -524,7 +570,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
@@ -964,8 +1010,28 @@
       </c>
     </row>
     <row r="55" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="2"/>
-      <c r="B55" s="1"/>
+      <c r="A55" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/ML_dataset_smapled/VLOOKUP 함수용 표.xlsx
+++ b/ML_dataset_smapled/VLOOKUP 함수용 표.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LG\OneDrive\Desktop\REF_Classification_For_Ingredient_Recognition\ML_dataset_smapled\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32AD6DC-326B-46F2-97D6-0587618E8526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBD70C9-898A-4A22-A964-5647486FA6ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="465" windowWidth="18510" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6960" yWindow="465" windowWidth="18570" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VLOOKUP 함수용 카테고리" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="82">
   <si>
     <t>ALCOHOL</t>
   </si>
@@ -284,6 +284,14 @@
   </si>
   <si>
     <t>GRAIN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>어육가공식품</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SIMPLE_PROCESSED</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -570,7 +578,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
@@ -1033,6 +1041,14 @@
         <v>79</v>
       </c>
     </row>
+    <row r="58" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
